--- a/supplier-claim-mgmt/原始文件/decisions/待确认决策表.xlsx
+++ b/supplier-claim-mgmt/原始文件/decisions/待确认决策表.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>索赔类型字典值以哪套为准？§4.1.1/§2.2.1『保内维修/服务活动/内部服务/特殊工单』，§4.1.4 结算明细『保修索赔/服务活动/内部服务/特殊事件』，文案不一。</t>
+          <t>索赔类型字典值以哪套为准？S4.1.1/S2.2.1『保内维修/服务活动/内部服务/特殊工单』，S4.1.4 结算明细『保修索赔/服务活动/内部服务/特殊事件』，文案不一。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>A｜统一为『保内维修/服务活动/内部服务/特殊工单』，§4.1.4 文案改齐。</t>
+          <t>A｜统一为『保内维修/服务活动/内部服务/特殊工单』，S4.1.4 文案改齐。</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>列表行按钮显示条件(§7.1)用『待审批』(【审核】按钮)与『审核驳回』(【编辑】按钮),但状态枚举(§5.1.1)是『待区域初审/待总部审核/已驳回』,无『待审批/审核驳回』值。按钮引用的是枚举外别名吗?</t>
+          <t>列表行按钮显示条件(S7.1)用『待审批』(【审核】按钮)与『审核驳回』(【编辑】按钮),但状态枚举(S5.1.1)是『待区域初审/待总部审核/已驳回』,无『待审批/审核驳回』值。按钮引用的是枚举外别名吗?</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>其它费用合计:§4.1.1字段说明『从工单中获取带入』(只读带入),但§2.2.1/§6.1『仅可修改物流费等其它费用』(可编辑)。其它费用是工单带入只读,还是允许人工新增/修改物流费等明细?</t>
+          <t>其它费用合计:S4.1.1字段说明『从工单中获取带入』(只读带入),但S2.2.1/S6.1『仅可修改物流费等其它费用』(可编辑)。其它费用是工单带入只读,还是允许人工新增/修改物流费等明细?</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -855,17 +855,17 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>可发起索赔的工单状态到底是【已完工】还是【已结算】？§2.2.1/§3.1.1 与流程图写『已完工』，§5.2 校验字典与 §7.2 页面写『已结算』，二者互斥。</t>
+          <t>可发起索赔的工单状态到底是【已完工】还是【已结算】？S2.2.1/S3.1.1 与流程图写『已完工』，S5.2 校验字典与 S7.2 页面写『已结算』，二者互斥。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>以【已完工】为准（§5.2/§7.2 属笔误）/以【已结算】为准（工单结算后才可索赔）</t>
+          <t>以【已完工】为准（S5.2/S7.2 属笔误）/以【已结算】为准（工单结算后才可索赔）</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>A｜以【已完工】为准（§5.2/§7.2『已结算』属笔误改正）。</t>
+          <t>A｜以【已完工】为准（S5.2/S7.2『已结算』属笔误改正）。</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>§2.2.1『根据工单类型关联显示索赔类型』,但工单分类(乘用车/商用车/储能/汽车电子/其他)与索赔类型(保内维修/服务活动/内部服务/特殊工单)是不同维度,二者映射关系未给。索赔类型是工单带出(按何映射)还是人工选择?</t>
+          <t>S2.2.1『根据工单类型关联显示索赔类型』,但工单分类(乘用车/商用车/储能/汽车电子/其他)与索赔类型(保内维修/服务活动/内部服务/特殊工单)是不同维度,二者映射关系未给。索赔类型是工单带出(按何映射)还是人工选择?</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -941,17 +941,17 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>条件必填规则(§3.2)要求电池包SN(24位)、汽车电子旧件条码、序列号、VIN等,闪欣索赔单字段表(§4.2.2)也含维修类型/二级维修类型/SN;但服务商索赔单字段表(§4.1.1)完全没有这些字段。这些SN/维修类型在服务商发起索赔时是工单带入还是服务商录入?落在哪张表?</t>
+          <t>条件必填规则(S3.2)要求电池包SN(24位)、汽车电子旧件条码、序列号、VIN等,闪欣索赔单字段表(S4.2.2)也含维修类型/二级维修类型/SN;但服务商索赔单字段表(S4.1.1)完全没有这些字段。这些SN/维修类型在服务商发起索赔时是工单带入还是服务商录入?落在哪张表?</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>维修类型/SN/条码由关联工单带入服务商索赔单(只读),§4.1.1字段表遗漏应补/由服务商在索赔单录入(条件必填)</t>
+          <t>维修类型/SN/条码由关联工单带入服务商索赔单(只读),S4.1.1字段表遗漏应补/由服务商在索赔单录入(条件必填)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>A｜维修类型/SN/条码由关联工单带入服务商索赔单（只读），§4.1.1 字段表补齐。</t>
+          <t>A｜维修类型/SN/条码由关联工单带入服务商索赔单（只读），S4.1.1 字段表补齐。</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>§3.2旧件回运:默认发售后就近仓、可选发闪欣仓,售后仓『仅点确认(无扫码)』、闪欣仓『支持扫码』;提交索赔需已发起回运(在途即可提交)。未定义:目的地由谁选(服务商/系统按备件属性)、售后仓无扫码时回运完成如何确认与凭据、『在途』能提交但回运未签收对后续结算是否有卡点。</t>
+          <t>S3.2旧件回运:默认发售后就近仓、可选发闪欣仓,售后仓『仅点确认(无扫码)』、闪欣仓『支持扫码』;提交索赔需已发起回运(在途即可提交)。未定义:目的地由谁选(服务商/系统按备件属性)、售后仓无扫码时回运完成如何确认与凭据、『在途』能提交但回运未签收对后续结算是否有卡点。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>§9.3数据范围与§5.2校验引用状态『待责任判定』(质量部仅操作该状态外采件),但索赔单状态枚举(§5.1.1)无此状态。外采件业务审核通过后进入质量判责环节时索赔单处于何状态?判责与『进入待结算』是串行阻塞还是并行?</t>
+          <t>S9.3数据范围与S5.2校验引用状态『待责任判定』(质量部仅操作该状态外采件),但索赔单状态枚举(S5.1.1)无此状态。外采件业务审核通过后进入质量判责环节时索赔单处于何状态?判责与『进入待结算』是串行阻塞还是并行?</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>索赔单驳回后:§2.2.1『逐级驳回』,§6.4『退回服务商,重新提交后按原流程从头开始流转』。驳回是逐级退回上一环节还是一律退回服务商草稿/驳回态?重提后从区域初审还是从被驳回环节继续?</t>
+          <t>索赔单驳回后:S2.2.1『逐级驳回』,S6.4『退回服务商,重新提交后按原流程从头开始流转』。驳回是逐级退回上一环节还是一律退回服务商草稿/驳回态?重提后从区域初审还是从被驳回环节继续?</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>重复索赔校验引用状态『已关闭』(§3.2『非已关闭』;§5.2『非已关闭、已作废』),但 §5.1.1 状态枚举无『已关闭』,只有『已拒绝/已作废/已结算』。『已关闭』对应哪个态?可重新发起的前置态是哪些?</t>
+          <t>重复索赔校验引用状态『已关闭』(S3.2『非已关闭』;S5.2『非已关闭、已作废』),但 S5.1.1 状态枚举无『已关闭』,只有『已拒绝/已作废/已结算』。『已关闭』对应哪个态?可重新发起的前置态是哪些?</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1242,17 +1242,17 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>闪欣侧付款:§2.2.5『自动推送财务系统发起付款申请、财务审批』暗示外部财务系统,但§6.8审批链(经办会计→财务经理→出纳→总账)与§7.9审批弹窗又像系统内审批流。闪欣侧付款审批是本系统内建审批流,还是推送外部财务系统审批?</t>
+          <t>闪欣侧付款:S2.2.5『自动推送财务系统发起付款申请、财务审批』暗示外部财务系统,但S6.8审批链(经办会计→财务经理→出纳→总账)与S7.9审批弹窗又像系统内审批流。闪欣侧付款审批是本系统内建审批流,还是推送外部财务系统审批?</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>闪欣侧付款审批为本系统内建可配置审批流(§6.8/§7.9),不对接外部财务系统/推送外部财务系统审批</t>
+          <t>闪欣侧付款审批为本系统内建可配置审批流(S6.8/S7.9),不对接外部财务系统/推送外部财务系统审批</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>A｜闪欣侧付款审批为本系统内建可配置审批流（§6.8/§7.9），不对接外部财务系统。</t>
+          <t>A｜闪欣侧付款审批为本系统内建可配置审批流（S6.8/S7.9），不对接外部财务系统。</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>付款申请单:§2.2.5『由结算单确认后自动生成并推送财务系统,无需人工新建/提交』;但§7.5/§7.6有手动『申请付款』按钮跳转付款单新增页,§7.11有【新增】按钮,§7.12是完整手工填写(开户行/账号/账户名)编辑页。付款申请单到底是自动生成还是人工新增填写?</t>
+          <t>付款申请单:S2.2.5『由结算单确认后自动生成并推送财务系统,无需人工新建/提交』;但S7.5/S7.6有手动『申请付款』按钮跳转付款单新增页,S7.11有【新增】按钮,S7.12是完整手工填写(开户行/账号/账户名)编辑页。付款申请单到底是自动生成还是人工新增填写?</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>系统按结算单自动生成付款申请(带出收款信息),人工仅补充/确认后提交/人工在§7.12新增页手工录入收款账户等并提交</t>
+          <t>系统按结算单自动生成付款申请(带出收款信息),人工仅补充/确认后提交/人工在S7.12新增页手工录入收款账户等并提交</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1543,17 +1543,17 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>付款审批分级的金额档位与各档审批链是否为最终口径?§6.8 标注『举例』。请确认&lt;5万/5万~20万/≥20万 三档节点链是否正式采用,含边界(=5万归哪档,已按&lt;与&gt;=划分)。</t>
+          <t>付款审批分级的金额档位与各档审批链是否为最终口径?S6.8 标注『举例』。请确认&lt;5万/5万~20万/≥20万 三档节点链是否正式采用,含边界(=5万归哪档,已按&lt;与&gt;=划分)。</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>采纳 §6.8 三档链为正式规则/档位/链路待财务重新给定,先按 §6.8 Mock</t>
+          <t>采纳 S6.8 三档链为正式规则/档位/链路待财务重新给定,先按 S6.8 Mock</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>A｜采纳 §6.8 三档金额线为正式规则，并在结算基础配置中可配置。</t>
+          <t>A｜采纳 S6.8 三档金额线为正式规则，并在结算基础配置中可配置。</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>付款申请单是否有『已作废』状态？§5.1.7 枚举五态无『已作废』，但 §7.11/§7.13 有作废操作与『已作废-灰色』标签。请补齐状态全集。</t>
+          <t>付款申请单是否有『已作废』状态？S5.1.7 枚举五态无『已作废』，但 S7.11/S7.13 有作废操作与『已作废-灰色』标签。请补齐状态全集。</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>责任判定结果完整字典值？四处不一致：含/不含『内部责任』，且『内部责任』vs『闪欣内部责任』文案不同；§7.2 弹窗下拉仅『供应商/服务商』两项。判定是否含内部责任、共几项？</t>
+          <t>责任判定结果完整字典值？四处不一致：含/不含『内部责任』，且『内部责任』vs『闪欣内部责任』文案不同；S7.2 弹窗下拉仅『供应商/服务商』两项。判定是否含内部责任、共几项？</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>A｜三项：供应商责任/服务商责任/内部责任；§7.2 弹窗补内部责任。</t>
+          <t>A｜三项：供应商责任/服务商责任/内部责任；S7.2 弹窗补内部责任。</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -1715,17 +1715,17 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>正数结算顺序不一致:§2.2.3『确认结算即代表发票核验无误并自动推送财务(不单独提交付款申请)』;§7.6/§3.1.3 却是分立按钮『开票→发票确认→确认结算→申请付款(跳付款单)』且有独立付款申请单模块。确认结算是否自动生成付款申请,还是需人工申请付款?</t>
+          <t>正数结算顺序不一致:S2.2.3『确认结算即代表发票核验无误并自动推送财务(不单独提交付款申请)』;S7.6/S3.1.3 却是分立按钮『开票→发票确认→确认结算→申请付款(跳付款单)』且有独立付款申请单模块。确认结算是否自动生成付款申请,还是需人工申请付款?</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>分立:发票确认→(闪欣侧)人工申请付款生成付款单进审批(§7/§2.2.5)/确认结算自动推财务不单独申请(§2.2.3/欣旺达侧)</t>
+          <t>分立:发票确认→(闪欣侧)人工申请付款生成付款单进审批(S7/S2.2.5)/确认结算自动推财务不单独申请(S2.2.3/欣旺达侧)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>A｜分立：发票确认后（闪欣侧）人工申请付款生成付款单进审批（§7/§2.2.5）。</t>
+          <t>A｜分立：发票确认后（闪欣侧）人工申请付款生成付款单进审批（S7/S2.2.5）。</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>结算应付=审核通过索赔应付 - 该主体周期内责任抵扣金额。但『责任抵扣单/抵扣金额』如何算未定义:抵扣金额=对应索赔全额还是按§4.1.1『责任方承担比例』折算?抵扣单与结算单的周期如何匹配(同周期/跨周期滚动)?</t>
+          <t>结算应付=审核通过索赔应付 - 该主体周期内责任抵扣金额。但『责任抵扣单/抵扣金额』如何算未定义:抵扣金额=对应索赔全额还是按S4.1.1『责任方承担比例』折算?抵扣单与结算单的周期如何匹配(同周期/跨周期滚动)?</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>流程图『通知开票→是否白名单→N:账单挂起/调整白名单』。但(1)结算状态枚举(§5.1.6)无『账单挂起』态;(2)『白名单』与§2.2.3/§2.2.6『服务商开票权限配置』是否同一概念未挑明。非白名单时结算单挂起在什么状态、如何恢复?</t>
+          <t>流程图『通知开票→是否白名单→N:账单挂起/调整白名单』。但(1)结算状态枚举(S5.1.6)无『账单挂起』态;(2)『白名单』与S2.2.3/S2.2.6『服务商开票权限配置』是否同一概念未挑明。非白名单时结算单挂起在什么状态、如何恢复?</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>负数结算单对账后处于什么状态？§7.5 按钮『强制结算(仅负数已对账状态)』引用了『负数已对账』，但 §5.1.6 枚举无此值；负数线无待开票，从『待对账』到『已结算』的中间态未定义。</t>
+          <t>负数结算单对账后处于什么状态？S7.5 按钮『强制结算(仅负数已对账状态)』引用了『负数已对账』，但 S5.1.6 枚举无此值；负数线无待开票，从『待对账』到『已结算』的中间态未定义。</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>欣旺达-闪欣结算单是『统一生成一张不拆分开票、内部分账交财务共享/OA』，还是『必须按归属维度拆分生成多张结算单』？§6.7 同段两句直接矛盾。</t>
+          <t>欣旺达-闪欣结算单是『统一生成一张不拆分开票、内部分账交财务共享/OA』，还是『必须按归属维度拆分生成多张结算单』？S6.7 同段两句直接矛盾。</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>闪欣向欣旺达索赔单是『业务审核通过后系统逐单自动生成(非汇总)』还是『索赔专员定期从池中勾选汇总生成』?§2.2.2 与 §3.1.2 口径相反。</t>
+          <t>闪欣向欣旺达索赔单是『业务审核通过后系统逐单自动生成(非汇总)』还是『索赔专员定期从池中勾选汇总生成』?S2.2.2 与 S3.1.2 口径相反。</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>逐单自动生成(§2.2.2/§6.2),专员补附件后提交/专员勾选汇总生成(§3.1.2),多明细合一单</t>
+          <t>逐单自动生成(S2.2.2/S6.2),专员补附件后提交/专员勾选汇总生成(S3.1.2),多明细合一单</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>A｜业务审核通过后逐单自动生成（§2.2.2/§6.2），专员补附件后提交。</t>
+          <t>A｜业务审核通过后逐单自动生成（S2.2.2/S6.2），专员补附件后提交。</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>闪欣向欣旺达索赔单工时费合计:字段说明(§4.2.2)为『根据工单工时费和索赔系数计算』(再乘一层系数),但§6.1明确『外采备件索赔金额=对应服务商索赔单工时费+其它费用』(直接等于服务商侧,不再乘系数)。闪欣索赔金额是否对服务商金额再乘一次索赔系数?</t>
+          <t>闪欣向欣旺达索赔单工时费合计:字段说明(S4.2.2)为『根据工单工时费和索赔系数计算』(再乘一层系数),但S6.1明确『外采备件索赔金额=对应服务商索赔单工时费+其它费用』(直接等于服务商侧,不再乘系数)。闪欣索赔金额是否对服务商金额再乘一次索赔系数?</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>闪欣金额=服务商对应金额,不再乘系数(依§6.1)/闪欣侧对工时费再乘欣旺达索赔系数(依§4.2.2)</t>
+          <t>闪欣金额=服务商对应金额,不再乘系数(依S6.1)/闪欣侧对工时费再乘欣旺达索赔系数(依S4.2.2)</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>A｜闪欣索赔金额=服务商对应金额，不再乘系数（依 §6.1）。</t>
+          <t>A｜闪欣索赔金额=服务商对应金额，不再乘系数（依 S6.1）。</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2145,17 +2145,17 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>维修/工单分类字典值？§4.2.2 维修类型『乘用车/商用车/其他』，§3.2 工单分类『乘用车/商用车/储能/汽车电子/其他』——储能、汽车电子是否为一级分类？与二级维修类型如何级联？</t>
+          <t>维修/工单分类字典值？S4.2.2 维修类型『乘用车/商用车/其他』，S3.2 工单分类『乘用车/商用车/储能/汽车电子/其他』——储能、汽车电子是否为一级分类？与二级维修类型如何级联？</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>一级=§3.2 五类，§4.2.2 简化表述改齐/一级=三类，储能/汽车电子归入『其他』二级</t>
+          <t>一级=S3.2 五类，S4.2.2 简化表述改齐/一级=三类，储能/汽车电子归入『其他』二级</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>A｜一级分类=§3.2 五类（乘用车/商用车/储能/汽车电子/其他），§4.2.2 简化表述改齐。</t>
+          <t>A｜一级分类=S3.2 五类（乘用车/商用车/储能/汽车电子/其他），S4.2.2 简化表述改齐。</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>车辆VIN码:§4.2.2『是否必填』列标『否』,字段说明却写『二级维修类型选整车维修必填,17位』,且『内部需求场景无』。到底条件必填还是选填?</t>
+          <t>车辆VIN码:S4.2.2『是否必填』列标『否』,字段说明却写『二级维修类型选整车维修必填,17位』,且『内部需求场景无』。到底条件必填还是选填?</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>闪欣索赔单字段(§4.2.2)『审核结果』枚举含『部分通过』,但审批操作(§2.2.2)只有通过/驳回/拒绝,状态枚举(§5.1.3)也无对应态。欣旺达『部分通过』时索赔单进入什么状态、金额如何按通过部分调整、后续结算以哪个金额为准?</t>
+          <t>闪欣索赔单字段(S4.2.2)『审核结果』枚举含『部分通过』,但审批操作(S2.2.2)只有通过/驳回/拒绝,状态枚举(S5.1.3)也无对应态。欣旺达『部分通过』时索赔单进入什么状态、金额如何按通过部分调整、后续结算以哪个金额为准?</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>抵扣基数 claim_liable_amount 口径：§9 未 narrow vs §8.3 外采件仅工时+其它</t>
+          <t>抵扣基数 claim_liable_amount 口径：S9 未 narrow vs S8.3 外采件仅工时+其它</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -2669,17 +2669,17 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>★备件管理费是否计入向欣旺达/闪欣结算金额(§9含 vs 原型不含·真冲突)</t>
+          <t>★备件管理费是否计入向欣旺达/闪欣结算金额(S9含 vs 原型不含·真冲突)</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>暂按含(§9选项A)；A含(=服务商单总额)/B不含(仅工时+其它)</t>
+          <t>暂按含(S9选项A)；A含(=服务商单总额)/B不含(仅工时+其它)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>备件管理费计入向欣旺达/闪欣结算金额（§9 选项A，=服务商单总额）；与结算 B5 同口径。</t>
+          <t>备件管理费计入向欣旺达/闪欣结算金额（S9 选项A，=服务商单总额）；与结算 B5 同口径。</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>§2 财务扣减 vs §6.4 索赔员发起未挑明；确认流程分工</t>
+          <t>S2 财务扣减 vs S6.4 索赔员发起未挑明；确认流程分工</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>§10枚举独立值/原型09 vs §4.4/§7『退回待提交』；请拍板</t>
+          <t>S10枚举独立值/原型09 vs S4.4/S7『退回待提交』；请拍板</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>驳回后回写『退回待提交』再走（§4.4/§7），不设 REJECTED 独立驻留态。</t>
+          <t>驳回后回写『退回待提交』再走（S4.4/S7），不设 REJECTED 独立驻留态。</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3645,93 +3645,512 @@
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="7" t="inlineStr">
+    <row r="74" ht="120" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>D-配置-B2</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>配置维护·生效日录入</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>结算基础配置维护侧补设计时暴露：settle_period_config/invoice_whitelist/claim_coefficient 均有 effective_from 列且消费侧按『effective_from&lt;=当前取最新』选行，但原型 12 未提供生效日录入控件，PRD 只给 A-16『变更仅对下一周期/新单生效、不回溯』未给精确生效日算法与录入方式（人工选日 vs 系统按下一周期起始自动写），且维护是覆盖更新同一行还是追加新生效行未明说（F-CFG-01/02/04）</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>建议产品明确：(a) 生效日是否人工录入、默认值口径；(b) 维护采用追加新生效行（保留历史供追溯、与消费侧取最新自洽）还是覆盖更新；本轮详设按『追加新生效行 + effective_from 写入』标指针，具体口径待定稿</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>待文档</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>配置维护侧补设计（缺口反查 G-CFG-1）暴露</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>d2.D-配置-B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>E-索赔-B1</t>
         </is>
       </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>责任判定校验</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>liabilityDesc 判责说明必填≤200，但错误码表无专属码、走通用 400（F-CLAIM-08）</t>
         </is>
       </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>建议为判责说明为空/超长补专属业务错误码，或确认沿用通用 400</t>
         </is>
       </c>
-      <c r="F74" s="5" t="inlineStr">
+      <c r="F75" s="5" t="inlineStr">
         <is>
           <t>接受走通用 400（参数校验不通过），不新增 liabilityDesc 专属错误码。</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
         <is>
           <t>G阶段暴露·次要</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>e.E-索赔-B1</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="45" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>D-付款-B5</t>
         </is>
       </c>
-      <c r="B75" s="4" t="inlineStr">
+      <c r="B76" s="4" t="inlineStr">
         <is>
           <t>待文档</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>原型同步</t>
         </is>
       </c>
-      <c r="D75" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>付款原型 09/10 仍展示旧『审批驳回/已退回申请人』独立驻留态，与已裁决 D-付款-D1（驳回直接回退待提交、不设 REJECTED 驻留态）矛盾</t>
         </is>
       </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>原型文档待修订同步至裁决口径；用例已按 D-付款-D1 拆解，不影响正确性</t>
         </is>
       </c>
-      <c r="F75" s="5" t="inlineStr"/>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="F76" s="5" t="inlineStr"/>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>待文档</t>
         </is>
       </c>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H76" s="5" t="inlineStr">
         <is>
           <t>G阶段暴露·原型待同步</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>d2.D-付款-B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="75" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>D-索赔-B9</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>服务商索赔单·分类列</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>claim_order 无 repair_type/sub_repair_type/serial_no/vin/province_city 列，但 PRD A-10(只读带入)/A-14(汽车电子工时把关)/A-39(条件必填场景触发)都依赖这组车辆/维修分类信息——是否给 claim_order 补这组列(与 xw_claim_order 对齐)？</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>建议加列。未加前 F-CLAIM-01 的 A-10 带出、A-14 汽车电子把关、A-39 场景条件必填均无数据支撑。加列=建表变更，须组长审定。</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】加列：claim_order 补 repair_type/sub_repair_type/serial_no/vin/province_city（与 xw_claim_order 对齐），支撑 A-10 带出/A-14 汽车电子把关/A-39 场景条件必填。</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>d2.D-索赔-B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>D-索赔-B10</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>服务商索赔单·判责留痕</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>claim_audit_record.audit_stage 枚举缺『责任判定』阶段码；判责留痕已补进 LLD/契约，但阶段码取值待定。</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>建议 audit_stage 增『责任判定』码；定码前留痕的 audit_stage 值悬空。</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】audit_stage 增『责任判定』(LIABILITY) 阶段码，判责留痕用此值。</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>d2.D-索赔-B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="45" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>D-索赔-B11</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>服务商索赔单·备件销售价</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>claim_fee_part 无 sale_price 列，mgmt_fee=销售价×系数 的销售价用完即弃、事后不可复核。是否加 sale_price 列落库？</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>建议加列以保金额可追溯。加列=建表变更。</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】claim_fee_part 加 sale_price 列落库，mgmt_fee 派生可追溯。</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>d2.D-索赔-B11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="75" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>D-向欣-B5</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>向欣旺达·外采件金额纳入</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>PRD S8.3/S9/A-37 要求外采件『工时费+其它费用』纳入向欣旺达索赔，S6.1/A-6『主责件唯一决定流向』又倾向不纳入——PRD 内部矛盾。两份 LLD 现按 claim_target='XW' 生成、排除外采件（静默选边）。</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>请裁决：纳入→补外采件向欣单/明细生成路径(生成源/金额口径/是否独立单)；不纳入→废止/修订 S9 该式并登记显式裁决。确认前不擅自实现纳入。</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK·真实业务须产品定】本期按不纳入：向欣旺达单仅欣旺达件(claim_target=XW)，外采件工时+其它仅走服务商结算；S9 该式本期修订为『仅欣旺达件』。</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>d2.D-向欣-B5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="90" customHeight="1">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>D-结算-B7</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>结算·质保金账户建账</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>质保金账户建账时机 + 初始余额/INIT 入账来源 PRD 未定（S8.9 只写余额/流水/归属）。OP11 强扣读 balance，但账户何时建、余额从哪来无据。</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>建议明确：账户建账触发(服务商开户/首次入账/首次强扣兜底) + 初始余额来源(缴纳/划拨)。定前 LLD 已按『账户须先存在、不存在报 SET_4009、不隐式建账』兜底，不臆造入账。</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK·真实业务须产品定】账户在服务商首次质保金入账时建账；初始余额由 INIT 流水入账（服务商缴纳/上游划拨），balance 从流水累计。</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>d2.D-结算-B7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="45" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>D-结算-B8</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>结算·质保金冻结/充值</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>质保金 RECHARGE 充值入口/发起方(PRD 无功能点)、账户 FROZEN 态迁移与『冻结时 OP11 强扣是否放行』、frozen_amount 冻结业务——本期是否启用均 PRD 未定。</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>本期 LLD 按 frozen_amount 恒 0、账户恒 NORMAL、无充值接口 兜底；是否本期启用请产品定。</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】本期不启用充值/冻结：frozen_amount 恒 0、账户恒 NORMAL、无充值入口，V2 再补。</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>d2.D-结算-B8</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="75" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>D-付款-B6</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>付款·审批链结构</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>payment_approval_flow_config.node_chain DDL 注为『有序审批角色链』，但 LLD/契约把每元素当『节点名+角色』两属性落 payment_approval_node.node_name/approver_role。若 node_chain 是纯角色数组，node_name 无真实来源。</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>请定 node_chain 结构：纯角色数组(需定 node_name 取值规则) vs {节点名,角色}对象数组(需统一 schema 注释)。</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】node_chain 定为 {节点名,角色} 对象数组，统一 schema 注释；node_name/approver_role 各取对象字段。</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>d2.D-付款-B6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="45" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>D-付款-B7</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>付款·账户名二次确认</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>账户名与 payee_name 不一致需『已二次确认』才能提交，但 schema 无二次确认标记列，后端无从判定确认是否完成。</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>请定落点：提交入参带确认标记 / 仅前端拦截后端不复校 / 加持久化列。</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】提交入参带 nameConfirmed 标记，后端据此放行；不加持久化列。</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>已确认</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>d2.D-付款-B7</t>
         </is>
       </c>
     </row>
@@ -3741,7 +4160,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待确认,已确认,待文档,待契约,自动定论"</formula1>
     </dataValidation>
   </dataValidations>

--- a/supplier-claim-mgmt/原始文件/decisions/待确认决策表.xlsx
+++ b/supplier-claim-mgmt/原始文件/decisions/待确认决策表.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>服务商索赔管理 · 待确认决策表（待产品逐条签）</t>
+          <t>服务商索赔单 · 待确认决策表（待产品逐条签）</t>
         </is>
       </c>
     </row>
@@ -2608,125 +2608,125 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>D-向欣-B1</t>
+          <t>E-通用-B1</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>待文档</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>向欣旺达·作废</t>
+          <t>批量审核</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>PENDING_AUDIT(待审核)能否撤回作废</t>
+          <t>批量审核语义未细化：批哪些状态、仅批量通过还是含批量驳回、权限与逐节点审批的关系、成功/失败明细结构均未定（F-CLAIM-10/F-PAY-05，契约仅『部分成功部分失败』）</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>仅 DRAFT 可作废</t>
+          <t>建议明确批量审核适用状态与动作（通过/驳回）、权限、返回明细结构；本期用例按通用规格行为级覆盖</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>仅 DRAFT 可作废；PENDING_AUDIT 不可撤回作废。</t>
+          <t>延到开发：本期批量审核按通用规格实现（勾选同状态单据批量执行、部分成功部分失败返回明细）；具体可批状态/是否含批量驳回/权限细则在开发对应功能前回看细化。</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>待文档</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>G阶段暴露·影响开发实现</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>d2.D-向欣-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>D-向欣-B2</t>
+          <t>e.E-通用-B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>E-通用-B2</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>待文档</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>向欣旺达/闪欣·金额口径</t>
+          <t>列表导出</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>★备件管理费是否计入向欣旺达/闪欣结算金额(S9含 vs 原型不含·真冲突)</t>
+          <t>『通用列表导出规格』被各模块引用但从未具体定义：导出字段范围、数据范围过滤口径、异步任务/进度轮询结构（F-CLAIM-09 等）</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>暂按含(S9选项A)；A含(=服务商单总额)/B不含(仅工时+其它)</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>备件管理费计入向欣旺达/闪欣结算金额（S9 选项A，=服务商单总额）；与结算 B5 同口径。</t>
-        </is>
-      </c>
+          <t>建议在 conventions 补一份通用列表查询/导出规格（导出=当前筛选列表字段+同列表数据范围过滤+异步任务），开发前定稿</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr"/>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>已确认</t>
+          <t>待文档</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>★真业务·勿默认·=结算B5同口径</t>
+          <t>G阶段暴露·可从列表字段派生</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>d2.D-向欣-B2</t>
+          <t>e.E-通用-B2</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>D-向欣-B3</t>
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>E-索赔-B1</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>向欣旺达·提交校验</t>
+          <t>责任判定校验</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>A-39 条件必填(电池包SN/序列号/VIN17)提交时是否硬卡</t>
+          <t>liabilityDesc 判责说明必填≤200，但错误码表无专属码、走通用 400（F-CLAIM-08）</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Mock 未带出放行；真库接上改硬校验</t>
+          <t>建议为判责说明为空/超长补专属业务错误码，或确认沿用通用 400</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>本期 Mock 未带出放行；真库接上后改硬校验。</t>
+          <t>接受走通用 400（参数校验不通过），不新增 liabilityDesc 专属错误码。</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
@@ -2736,44 +2736,44 @@
       </c>
       <c r="H53" s="5" t="inlineStr">
         <is>
-          <t>待挂载</t>
+          <t>G阶段暴露·次要</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>d2.D-向欣-B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>D-向欣-B4</t>
+          <t>e.E-索赔-B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="75" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>D-索赔-B9</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>向欣旺达·部分通过</t>
+          <t>服务商索赔单·分类列</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>部分通过核减明细是否结构化落库</t>
+          <t>claim_order 无 repair_type/sub_repair_type/serial_no/vin/province_city 列，但 PRD A-10(只读带入)/A-14(汽车电子工时把关)/A-39(条件必填场景触发)都依赖这组车辆/维修分类信息——是否给 claim_order 补这组列(与 xw_claim_order 对齐)？</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>记 claim_audit_record.remark 文本；确认是否需专表</t>
+          <t>建议加列。未加前 F-CLAIM-01 的 A-10 带出、A-14 汽车电子把关、A-39 场景条件必填均无数据支撑。加列=建表变更，须组长审定。</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>部分通过核减明细记 claim_audit_record.remark 文本，本期不建专表。</t>
+          <t>【MOCK】加列：claim_order 补 repair_type/sub_repair_type/serial_no/vin/province_city（与 xw_claim_order 对齐），支撑 A-10 带出/A-14 汽车电子把关/A-39 场景条件必填。</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -2781,1376 +2781,108 @@
           <t>已确认</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr"/>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>d2.D-向欣-B4</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>D-向欣-D1</t>
+          <t>d2.D-索赔-B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="45" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>D-索赔-B10</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>待文档</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>向欣旺达·明细唯一</t>
+          <t>服务商索赔单·判责留痕</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>uk_provider_claim 单列 UNIQUE 与软删/作废释放冲突</t>
+          <t>claim_audit_record.audit_stage 枚举缺『责任判定』阶段码；判责留痕已补进 LLD/契约，但阶段码取值待定。</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>按作废/删即释放占用设计，物理实现研发在 ddl 落实</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr"/>
+          <t>建议 audit_stage 增『责任判定』码；定码前留痕的 audit_stage 值悬空。</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】audit_stage 增『责任判定』(LIABILITY) 阶段码，判责留痕用此值。</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>待文档</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>研发向</t>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>d2.D-向欣-D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
+          <t>d2.D-索赔-B10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="45" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>D-结算-B1</t>
+          <t>D-索赔-B11</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>待文档</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>结算·归属时间</t>
+          <t>服务商索赔单·备件销售价</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>归属时间无专列(派生 claim_audit_record)</t>
+          <t>claim_fee_part 无 sale_price 列，mgmt_fee=销售价×系数 的销售价用完即弃、事后不可复核。是否加 sale_price 列落库？</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>建议加审批通过时间快照列</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr"/>
+          <t>建议加列以保金额可追溯。加列=建表变更。</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>【MOCK】claim_fee_part 加 sale_price 列落库，mgmt_fee 派生可追溯。</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>待文档</t>
+          <t>已确认</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>研发/schema向</t>
+          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>d2.D-结算-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>D-结算-B2</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>结算·确认阶段增删</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>确认阶段增删明细致应付=0/变号如何处理</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>需定：变号后重分正负线 / =0 走0元核销</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>变号后重分正负线；应付=0 走 0 元核销。</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>★业务</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>D-结算-B3</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>结算·开票</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>发票金额是否强校验=应付金额</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>建议强校验(不等不可核验)；确认是否允许差额</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>发票金额强校验=应付金额，不等不可核验，不允许差额。</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
-        <is>
-          <t>D-结算-B4</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>结算·强制结算</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>强制结算与质保金扣减是否两步/财务二次确认</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>S2 财务扣减 vs S6.4 索赔员发起未挑明；确认流程分工</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>强制结算与质保金扣减两步、财务二次确认：索赔员发起、财务执行扣减。</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>★业务</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B4</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
-        <is>
-          <t>D-结算-B5</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>结算·闪欣备件管理费</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>闪欣结算是否计入/展示备件管理费</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>见 D-向欣-B2 一并定(同口径)</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>闪欣结算计入并展示备件管理费，与 D-向欣-B2 同口径。</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>★=向欣B2</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B5</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="60" customHeight="1">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>D-结算-B6</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>结算·迟到数据</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>原归属周期结算单已生成后才进入待结算的索赔/抵扣，应如何消费</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>建议选「滚入下一执行周期，保留原归属日供追溯」；备选=补开原周期单/重开原单（均需改唯一与已开票边界）</t>
-        </is>
-      </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>滚入下一执行周期，并保留原归属日期供追溯；不补开原周期单、不重开已生成结算单。</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>产品确认方案1；下一执行周期消费，源单归属日期不改</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B6</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>D-付款-D1</t>
-        </is>
-      </c>
-      <c r="B62" s="4" t="inlineStr">
-        <is>
-          <t>裁决</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>付款·驳回处置</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>驳回后 REJECTED 独立驻留态 vs 回写待提交再走</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>S10枚举独立值/原型09 vs S4.4/S7『退回待提交』；请拍板</t>
-        </is>
-      </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>驳回后回写『退回待提交』再走（S4.4/S7），不设 REJECTED 独立驻留态。</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>d2.D-付款-D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>D-付款-B1</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
-        <is>
-          <t>付款·重提</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>payment_approval_node 无轮次列，重提旧节点历史如何处置</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
-        <is>
-          <t>软删旧节点后重建 or 表加 round 轮次列</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>研发向</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>D-付款-B2</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>付款·费用归属</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>fee_owner 恒 SHANXIN vs 从结算派生</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>确认恒 'SHANXIN'(闪欣付服务商)</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>fee_owner 恒 'SHANXIN'（闪欣付服务商）。</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>scope已收敛</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>D-付款-B3</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>付款·发票信息</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>invoice_info_id 指向发票实体未登记(结算内联发票字段)</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>改存 settle_id/结算发票附件id，或本期置 NULL</t>
-        </is>
-      </c>
-      <c r="F65" s="5" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>研发向</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>D-付款-B4</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C66" s="5" t="inlineStr">
-        <is>
-          <t>付款·付款完成</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>付款 PAID 联动索赔单 SETTLED 是否同事务</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
-        <is>
-          <t>建议结算 SETTLED 与付款同事务，索赔单批量置位由结算归口</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>结算 SETTLED 与付款 PAID 同事务，索赔单批量置位由结算归口。</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B4</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="6" t="inlineStr">
-        <is>
-          <t>D-编码-D1</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>裁决</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
-        <is>
-          <t>编码·并发方案</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="inlineStr">
-        <is>
-          <t>号段/序列并发方案二选一</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
-        <is>
-          <t>裁决:序列表 doc_no_sequence+同事务行锁，不用 Redis(跳号)</t>
-        </is>
-      </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>序列表 doc_no_sequence + 同事务行锁，不用 Redis。</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>组长向</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>d2.D-编码-D1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
-        <is>
-          <t>D-编码-D2</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>裁决</t>
-        </is>
-      </c>
-      <c r="C68" s="5" t="inlineStr">
-        <is>
-          <t>编码·占号策略</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="inlineStr">
-        <is>
-          <t>回滚与占号</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr">
-        <is>
-          <t>裁决:提交成功才占号，回滚退号，无跳号</t>
-        </is>
-      </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>提交成功才占号，回滚退号，无跳号。</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>组长向</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>d2.D-编码-D2</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>D-编码-B1</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>编码·序列表</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t>doc_no_sequence 为新增表，需建表 SQL 经组长评审</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>产 ddl/doc_no_sequence.sql 标待组长审定，冻结前补</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr"/>
-      <c r="G69" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>待组长审定</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>d2.D-编码-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>D-编码-B2</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>编码·溢出</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>单前缀单日 &gt;9999 张溢出处理</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>本期抛异常告警拒绝(量级不触及)；需扩5位走变更登记</t>
-        </is>
-      </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>单前缀单日 &gt;9999 抛异常告警拒绝；扩 5 位走变更登记。</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H70" s="5" t="inlineStr"/>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>d2.D-编码-B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>E-通用-B1</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>批量审核</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>批量审核语义未细化：批哪些状态、仅批量通过还是含批量驳回、权限与逐节点审批的关系、成功/失败明细结构均未定（F-CLAIM-10/F-PAY-05，契约仅『部分成功部分失败』）</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>建议明确批量审核适用状态与动作（通过/驳回）、权限、返回明细结构；本期用例按通用规格行为级覆盖</t>
-        </is>
-      </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>延到开发：本期批量审核按通用规格实现（勾选同状态单据批量执行、部分成功部分失败返回明细）；具体可批状态/是否含批量驳回/权限细则在开发对应功能前回看细化。</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>G阶段暴露·影响开发实现</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>e.E-通用-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>E-通用-B2</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>列表导出</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>『通用列表导出规格』被各模块引用但从未具体定义：导出字段范围、数据范围过滤口径、异步任务/进度轮询结构（F-CLAIM-09 等）</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>建议在 conventions 补一份通用列表查询/导出规格（导出=当前筛选列表字段+同列表数据范围过滤+异步任务），开发前定稿</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="inlineStr"/>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>G阶段暴露·可从列表字段派生</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>e.E-通用-B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>D-配置-B1</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>配置字段校验</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>结算基础配置各页签字段级保存校验规则未定义：索赔系数取值范围、付款金额档区间连续/不重叠、审批链非空等（F-CFG-01，PRD/原型/决策仅『可维护』与生效范围）</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>建议产品补明确各配置项字段级校验规则；本期用例只覆盖权限门禁与生效范围/不回溯</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>延到开发：配置字段级校验按合理默认实现（系数&gt;0、金额档区间连续不重叠、审批链非空等），开发配置功能前回看定稿具体阈值。</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>G阶段暴露</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>d2.D-配置-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="120" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>D-配置-B2</t>
-        </is>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>配置维护·生效日录入</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>结算基础配置维护侧补设计时暴露：settle_period_config/invoice_whitelist/claim_coefficient 均有 effective_from 列且消费侧按『effective_from&lt;=当前取最新』选行，但原型 12 未提供生效日录入控件，PRD 只给 A-16『变更仅对下一周期/新单生效、不回溯』未给精确生效日算法与录入方式（人工选日 vs 系统按下一周期起始自动写），且维护是覆盖更新同一行还是追加新生效行未明说（F-CFG-01/02/04）</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>建议产品明确：(a) 生效日是否人工录入、默认值口径；(b) 维护采用追加新生效行（保留历史供追溯、与消费侧取最新自洽）还是覆盖更新；本轮详设按『追加新生效行 + effective_from 写入』标指针，具体口径待定稿</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="inlineStr"/>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>配置维护侧补设计（缺口反查 G-CFG-1）暴露</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>d2.D-配置-B2</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>E-索赔-B1</t>
-        </is>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>责任判定校验</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>liabilityDesc 判责说明必填≤200，但错误码表无专属码、走通用 400（F-CLAIM-08）</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
-        <is>
-          <t>建议为判责说明为空/超长补专属业务错误码，或确认沿用通用 400</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>接受走通用 400（参数校验不通过），不新增 liabilityDesc 专属错误码。</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>G阶段暴露·次要</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>e.E-索赔-B1</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>D-付款-B5</t>
-        </is>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>原型同步</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>付款原型 09/10 仍展示旧『审批驳回/已退回申请人』独立驻留态，与已裁决 D-付款-D1（驳回直接回退待提交、不设 REJECTED 驻留态）矛盾</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>原型文档待修订同步至裁决口径；用例已按 D-付款-D1 拆解，不影响正确性</t>
-        </is>
-      </c>
-      <c r="F76" s="5" t="inlineStr"/>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>待文档</t>
-        </is>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>G阶段暴露·原型待同步</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B5</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="75" customHeight="1">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>D-索赔-B9</t>
-        </is>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>服务商索赔单·分类列</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>claim_order 无 repair_type/sub_repair_type/serial_no/vin/province_city 列，但 PRD A-10(只读带入)/A-14(汽车电子工时把关)/A-39(条件必填场景触发)都依赖这组车辆/维修分类信息——是否给 claim_order 补这组列(与 xw_claim_order 对齐)？</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>建议加列。未加前 F-CLAIM-01 的 A-10 带出、A-14 汽车电子把关、A-39 场景条件必填均无数据支撑。加列=建表变更，须组长审定。</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK】加列：claim_order 补 repair_type/sub_repair_type/serial_no/vin/province_city（与 xw_claim_order 对齐），支撑 A-10 带出/A-14 汽车电子把关/A-39 场景条件必填。</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>d2.D-索赔-B9</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="45" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>D-索赔-B10</t>
-        </is>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>服务商索赔单·判责留痕</t>
-        </is>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>claim_audit_record.audit_stage 枚举缺『责任判定』阶段码；判责留痕已补进 LLD/契约，但阶段码取值待定。</t>
-        </is>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
-        <is>
-          <t>建议 audit_stage 增『责任判定』码；定码前留痕的 audit_stage 值悬空。</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK】audit_stage 增『责任判定』(LIABILITY) 阶段码，判责留痕用此值。</t>
-        </is>
-      </c>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>d2.D-索赔-B10</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="45" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>D-索赔-B11</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>服务商索赔单·备件销售价</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>claim_fee_part 无 sale_price 列，mgmt_fee=销售价×系数 的销售价用完即弃、事后不可复核。是否加 sale_price 列落库？</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>建议加列以保金额可追溯。加列=建表变更。</t>
-        </is>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK】claim_fee_part 加 sale_price 列落库，mgmt_fee 派生可追溯。</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
           <t>d2.D-索赔-B11</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="75" customHeight="1">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>D-向欣-B5</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>向欣旺达·外采件金额纳入</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>PRD S8.3/S9/A-37 要求外采件『工时费+其它费用』纳入向欣旺达索赔，S6.1/A-6『主责件唯一决定流向』又倾向不纳入——PRD 内部矛盾。两份 LLD 现按 claim_target='XW' 生成、排除外采件（静默选边）。</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="inlineStr">
-        <is>
-          <t>请裁决：纳入→补外采件向欣单/明细生成路径(生成源/金额口径/是否独立单)；不纳入→废止/修订 S9 该式并登记显式裁决。确认前不擅自实现纳入。</t>
-        </is>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK·真实业务须产品定】本期按不纳入：向欣旺达单仅欣旺达件(claim_target=XW)，外采件工时+其它仅走服务商结算；S9 该式本期修订为『仅欣旺达件』。</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>d2.D-向欣-B5</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="90" customHeight="1">
-      <c r="A81" s="6" t="inlineStr">
-        <is>
-          <t>D-结算-B7</t>
-        </is>
-      </c>
-      <c r="B81" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>结算·质保金账户建账</t>
-        </is>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>质保金账户建账时机 + 初始余额/INIT 入账来源 PRD 未定（S8.9 只写余额/流水/归属）。OP11 强扣读 balance，但账户何时建、余额从哪来无据。</t>
-        </is>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
-        <is>
-          <t>建议明确：账户建账触发(服务商开户/首次入账/首次强扣兜底) + 初始余额来源(缴纳/划拨)。定前 LLD 已按『账户须先存在、不存在报 SET_4009、不隐式建账』兜底，不臆造入账。</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK·真实业务须产品定】账户在服务商首次质保金入账时建账；初始余额由 INIT 流水入账（服务商缴纳/上游划拨），balance 从流水累计。</t>
-        </is>
-      </c>
-      <c r="G81" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B7</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="3" t="inlineStr">
-        <is>
-          <t>D-结算-B8</t>
-        </is>
-      </c>
-      <c r="B82" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>结算·质保金冻结/充值</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>质保金 RECHARGE 充值入口/发起方(PRD 无功能点)、账户 FROZEN 态迁移与『冻结时 OP11 强扣是否放行』、frozen_amount 冻结业务——本期是否启用均 PRD 未定。</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>本期 LLD 按 frozen_amount 恒 0、账户恒 NORMAL、无充值接口 兜底；是否本期启用请产品定。</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK】本期不启用充值/冻结：frozen_amount 恒 0、账户恒 NORMAL、无充值入口，V2 再补。</t>
-        </is>
-      </c>
-      <c r="G82" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>d2.D-结算-B8</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="75" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>D-付款-B6</t>
-        </is>
-      </c>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
-        <is>
-          <t>付款·审批链结构</t>
-        </is>
-      </c>
-      <c r="D83" s="5" t="inlineStr">
-        <is>
-          <t>payment_approval_flow_config.node_chain DDL 注为『有序审批角色链』，但 LLD/契约把每元素当『节点名+角色』两属性落 payment_approval_node.node_name/approver_role。若 node_chain 是纯角色数组，node_name 无真实来源。</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>请定 node_chain 结构：纯角色数组(需定 node_name 取值规则) vs {节点名,角色}对象数组(需统一 schema 注释)。</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK】node_chain 定为 {节点名,角色} 对象数组，统一 schema 注释；node_name/approver_role 各取对象字段。</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B6</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="45" customHeight="1">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>D-付款-B7</t>
-        </is>
-      </c>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>付款·账户名二次确认</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>账户名与 payee_name 不一致需『已二次确认』才能提交，但 schema 无二次确认标记列，后端无从判定确认是否完成。</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>请定落点：提交入参带确认标记 / 仅前端拦截后端不复校 / 加持久化列。</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>【MOCK】提交入参带 nameConfirmed 标记，后端据此放行；不加持久化列。</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>已确认</t>
-        </is>
-      </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>MOCK 模拟确认(跑流程用)·真实业务须产品复核</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>d2.D-付款-B7</t>
         </is>
       </c>
     </row>
@@ -4160,7 +2892,7 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待确认,已确认,待文档,待契约,自动定论"</formula1>
     </dataValidation>
   </dataValidations>
